--- a/Result/profitability/3522.xlsx
+++ b/Result/profitability/3522.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4825000000000002</v>
+        <v>-0.4675000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>40.21</v>
+        <v>40.50375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.71</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2725000000000001</v>
+        <v>-0.2800000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>37.6125</v>
+        <v>36.675</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.53</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1075000000000001</v>
+        <v>-0.2387500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>33.33750000000001</v>
+        <v>31.79625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.48</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1925000000000001</v>
+        <v>-0.1775000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>27.44625</v>
+        <v>27.345</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09625000000000009</v>
+        <v>0.002499999999999898</v>
       </c>
       <c r="N6" t="n">
-        <v>23.3275</v>
+        <v>24.2675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05999999999999989</v>
+        <v>-0.0150000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>21.15875</v>
+        <v>20.53625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1737499999999999</v>
+        <v>0.01749999999999989</v>
       </c>
       <c r="N8" t="n">
-        <v>17.55875</v>
+        <v>15.7125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3522</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>215</v>
+      </c>
+      <c r="D75" t="n">
+        <v>130</v>
+      </c>
+      <c r="E75" t="n">
+        <v>85</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-90</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-42.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-94</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-89</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.6087500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.285</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-14.77</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2723082595870207</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1237113402061856</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8100000000000023</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02010923535253228</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
